--- a/research/traditional_assets/database/data/tunisia/tunisia_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_food_wholesalers.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0776</v>
+        <v>0.0626</v>
       </c>
       <c r="E2">
-        <v>0.263</v>
+        <v>0.173</v>
       </c>
       <c r="G2">
-        <v>0.3448275862068966</v>
+        <v>0.4161735700197238</v>
       </c>
       <c r="H2">
-        <v>0.3448275862068966</v>
+        <v>0.4161735700197238</v>
       </c>
       <c r="I2">
-        <v>0.2903811252268603</v>
+        <v>0.3234714003944773</v>
       </c>
       <c r="J2">
-        <v>0.240978622103849</v>
+        <v>0.2775190254886524</v>
       </c>
       <c r="K2">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>0.3466424682395644</v>
+        <v>0.3944773175542406</v>
       </c>
       <c r="M2">
-        <v>0.666</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N2">
-        <v>0.03827586206896552</v>
+        <v>0.0431651376146789</v>
       </c>
       <c r="O2">
-        <v>0.3486910994764398</v>
+        <v>0.4705</v>
       </c>
       <c r="P2">
-        <v>0.666</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.03827586206896552</v>
+        <v>0.0431651376146789</v>
       </c>
       <c r="R2">
-        <v>0.3486910994764398</v>
+        <v>0.4705</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.59</v>
+        <v>0.349</v>
       </c>
       <c r="V2">
-        <v>0.2063218390804598</v>
+        <v>0.0160091743119266</v>
       </c>
       <c r="W2">
-        <v>0.1891089108910891</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="X2">
-        <v>0.08401885836837074</v>
+        <v>0.1307729739057063</v>
       </c>
       <c r="Y2">
-        <v>0.1050900525227184</v>
+        <v>0.05970321657048419</v>
       </c>
       <c r="Z2">
-        <v>0.5950966627065557</v>
+        <v>0.7337192474674386</v>
       </c>
       <c r="AA2">
-        <v>0.1434055737976248</v>
+        <v>0.2036210505394309</v>
       </c>
       <c r="AB2">
-        <v>0.08401885836837074</v>
+        <v>0.1307729739057063</v>
       </c>
       <c r="AC2">
-        <v>0.05938671542925404</v>
+        <v>0.07284807663372464</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-3.59</v>
+        <v>-0.349</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2599565532223027</v>
+        <v>-0.01626963777912451</v>
       </c>
       <c r="AK2">
-        <v>-0.5195369030390737</v>
+        <v>-0.03744233451346422</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.649</v>
+        <v>-0.68</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.725961538461538</v>
+        <v>-0.1685990338164251</v>
       </c>
       <c r="AQ2">
-        <v>-2.465331278890601</v>
+        <v>-2.411764705882353</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0776</v>
+        <v>0.0626</v>
       </c>
       <c r="E3">
-        <v>0.263</v>
+        <v>0.173</v>
       </c>
       <c r="G3">
-        <v>0.3448275862068966</v>
+        <v>0.4161735700197238</v>
       </c>
       <c r="H3">
-        <v>0.3448275862068966</v>
+        <v>0.4161735700197238</v>
       </c>
       <c r="I3">
-        <v>0.2903811252268603</v>
+        <v>0.3234714003944773</v>
       </c>
       <c r="J3">
-        <v>0.240978622103849</v>
+        <v>0.2775190254886524</v>
       </c>
       <c r="K3">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>0.3466424682395644</v>
+        <v>0.3944773175542406</v>
       </c>
       <c r="M3">
-        <v>0.666</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N3">
-        <v>0.03827586206896552</v>
+        <v>0.0431651376146789</v>
       </c>
       <c r="O3">
-        <v>0.3486910994764398</v>
+        <v>0.4705</v>
       </c>
       <c r="P3">
-        <v>0.666</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.03827586206896552</v>
+        <v>0.0431651376146789</v>
       </c>
       <c r="R3">
-        <v>0.3486910994764398</v>
+        <v>0.4705</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.59</v>
+        <v>0.349</v>
       </c>
       <c r="V3">
-        <v>0.2063218390804598</v>
+        <v>0.0160091743119266</v>
       </c>
       <c r="W3">
-        <v>0.1891089108910891</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="X3">
-        <v>0.08401885836837074</v>
+        <v>0.1307729739057063</v>
       </c>
       <c r="Y3">
-        <v>0.1050900525227184</v>
+        <v>0.05970321657048419</v>
       </c>
       <c r="Z3">
-        <v>0.5950966627065557</v>
+        <v>0.7337192474674386</v>
       </c>
       <c r="AA3">
-        <v>0.1434055737976248</v>
+        <v>0.2036210505394309</v>
       </c>
       <c r="AB3">
-        <v>0.08401885836837074</v>
+        <v>0.1307729739057063</v>
       </c>
       <c r="AC3">
-        <v>0.05938671542925404</v>
+        <v>0.07284807663372464</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.59</v>
+        <v>-0.349</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2599565532223027</v>
+        <v>-0.01626963777912451</v>
       </c>
       <c r="AK3">
-        <v>-0.5195369030390737</v>
+        <v>-0.03744233451346422</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.649</v>
+        <v>-0.68</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.725961538461538</v>
+        <v>-0.1685990338164251</v>
       </c>
       <c r="AQ3">
-        <v>-2.465331278890601</v>
+        <v>-2.411764705882353</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tunisia/tunisia_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_food_wholesalers.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0626</v>
+        <v>0.0701</v>
       </c>
       <c r="E2">
-        <v>0.173</v>
+        <v>0.158</v>
       </c>
       <c r="G2">
-        <v>0.4161735700197238</v>
+        <v>0.3808664259927798</v>
       </c>
       <c r="H2">
-        <v>0.4161735700197238</v>
+        <v>0.3808664259927798</v>
       </c>
       <c r="I2">
-        <v>0.3234714003944773</v>
+        <v>0.315884476534296</v>
       </c>
       <c r="J2">
-        <v>0.2775190254886524</v>
+        <v>0.2626248845604903</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="L2">
-        <v>0.3944773175542406</v>
+        <v>0.3862815884476534</v>
       </c>
       <c r="M2">
-        <v>0.9409999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="N2">
-        <v>0.0431651376146789</v>
+        <v>0.1589041095890411</v>
       </c>
       <c r="O2">
-        <v>0.4705</v>
+        <v>1.626168224299065</v>
       </c>
       <c r="P2">
-        <v>0.9409999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="Q2">
-        <v>0.0431651376146789</v>
+        <v>0.1589041095890411</v>
       </c>
       <c r="R2">
-        <v>0.4705</v>
+        <v>1.626168224299065</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.349</v>
+        <v>0.335</v>
       </c>
       <c r="V2">
-        <v>0.0160091743119266</v>
+        <v>0.01529680365296804</v>
       </c>
       <c r="W2">
-        <v>0.1904761904761905</v>
+        <v>0.2213029989658739</v>
       </c>
       <c r="X2">
-        <v>0.1307729739057063</v>
+        <v>0.128419909354234</v>
       </c>
       <c r="Y2">
-        <v>0.05970321657048419</v>
+        <v>0.09288308961163988</v>
       </c>
       <c r="Z2">
-        <v>0.7337192474674386</v>
+        <v>0.5943568286664521</v>
       </c>
       <c r="AA2">
-        <v>0.2036210505394309</v>
+        <v>0.1560928935162661</v>
       </c>
       <c r="AB2">
-        <v>0.1307729739057063</v>
+        <v>0.128419909354234</v>
       </c>
       <c r="AC2">
-        <v>0.07284807663372464</v>
+        <v>0.02767298416203212</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.349</v>
+        <v>-0.335</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.01626963777912451</v>
+        <v>-0.01553443079063297</v>
       </c>
       <c r="AK2">
-        <v>-0.03744233451346422</v>
+        <v>-0.03491401771756124</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.68</v>
+        <v>-0.824</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.1685990338164251</v>
+        <v>-0.1550925925925926</v>
       </c>
       <c r="AQ2">
-        <v>-2.411764705882353</v>
+        <v>-2.12378640776699</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0626</v>
+        <v>0.0701</v>
       </c>
       <c r="E3">
-        <v>0.173</v>
+        <v>0.158</v>
       </c>
       <c r="G3">
-        <v>0.4161735700197238</v>
+        <v>0.3808664259927798</v>
       </c>
       <c r="H3">
-        <v>0.4161735700197238</v>
+        <v>0.3808664259927798</v>
       </c>
       <c r="I3">
-        <v>0.3234714003944773</v>
+        <v>0.315884476534296</v>
       </c>
       <c r="J3">
-        <v>0.2775190254886524</v>
+        <v>0.2626248845604903</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="L3">
-        <v>0.3944773175542406</v>
+        <v>0.3862815884476534</v>
       </c>
       <c r="M3">
-        <v>0.9409999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="N3">
-        <v>0.0431651376146789</v>
+        <v>0.1589041095890411</v>
       </c>
       <c r="O3">
-        <v>0.4705</v>
+        <v>1.626168224299065</v>
       </c>
       <c r="P3">
-        <v>0.9409999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="Q3">
-        <v>0.0431651376146789</v>
+        <v>0.1589041095890411</v>
       </c>
       <c r="R3">
-        <v>0.4705</v>
+        <v>1.626168224299065</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.349</v>
+        <v>0.335</v>
       </c>
       <c r="V3">
-        <v>0.0160091743119266</v>
+        <v>0.01529680365296804</v>
       </c>
       <c r="W3">
-        <v>0.1904761904761905</v>
+        <v>0.2213029989658739</v>
       </c>
       <c r="X3">
-        <v>0.1307729739057063</v>
+        <v>0.128419909354234</v>
       </c>
       <c r="Y3">
-        <v>0.05970321657048419</v>
+        <v>0.09288308961163988</v>
       </c>
       <c r="Z3">
-        <v>0.7337192474674386</v>
+        <v>0.5943568286664521</v>
       </c>
       <c r="AA3">
-        <v>0.2036210505394309</v>
+        <v>0.1560928935162661</v>
       </c>
       <c r="AB3">
-        <v>0.1307729739057063</v>
+        <v>0.128419909354234</v>
       </c>
       <c r="AC3">
-        <v>0.07284807663372464</v>
+        <v>0.02767298416203212</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.349</v>
+        <v>-0.335</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01626963777912451</v>
+        <v>-0.01553443079063297</v>
       </c>
       <c r="AK3">
-        <v>-0.03744233451346422</v>
+        <v>-0.03491401771756124</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.68</v>
+        <v>-0.824</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.1685990338164251</v>
+        <v>-0.1550925925925926</v>
       </c>
       <c r="AQ3">
-        <v>-2.411764705882353</v>
+        <v>-2.12378640776699</v>
       </c>
     </row>
   </sheetData>
